--- a/templates/範本-秦皇傳說.xlsx
+++ b/templates/範本-秦皇傳說.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12285" activeTab="2"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12285"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -3177,52 +3177,41 @@
     <xf numFmtId="0" fontId="21" fillId="14" borderId="85" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="70" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="70" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3234,46 +3223,19 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="29" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="34" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="39" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3291,28 +3253,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3324,34 +3265,93 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="29" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="34" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="70" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="70" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="72" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3379,319 +3379,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="190500" cy="171450"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="image1.png"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="190500" cy="171450"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="image9.png"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="190500" cy="171450"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="image4.png"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="190500" cy="171450"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="image10.png"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="190500" cy="171450"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="6" name="image2.png"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="190500" cy="171450"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="7" name="image5.png"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="190500" cy="171450"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="8" name="image8.png"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>43</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="190500" cy="171450"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="9" name="image6.png"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>43</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="190500" cy="171450"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="10" name="image11.png"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>43</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="190500" cy="171450"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="11" name="image3.png"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>43</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="190500" cy="171450"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="12" name="image7.png"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId11" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3952,10 +3639,10 @@
       <c r="K2" s="1"/>
       <c r="L2" s="1"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="144" t="s">
+      <c r="N2" s="169" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="142"/>
+      <c r="O2" s="170"/>
       <c r="P2" s="7"/>
       <c r="Q2" s="7"/>
       <c r="R2" s="7"/>
@@ -3997,24 +3684,24 @@
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="145" t="s">
+      <c r="N3" s="171" t="s">
         <v>8</v>
       </c>
-      <c r="O3" s="134"/>
-      <c r="P3" s="134"/>
-      <c r="Q3" s="134"/>
-      <c r="R3" s="134"/>
-      <c r="S3" s="134"/>
-      <c r="T3" s="134"/>
-      <c r="U3" s="134"/>
-      <c r="V3" s="134"/>
-      <c r="W3" s="134"/>
-      <c r="X3" s="134"/>
-      <c r="Y3" s="134"/>
-      <c r="Z3" s="134"/>
-      <c r="AA3" s="134"/>
-      <c r="AB3" s="134"/>
-      <c r="AC3" s="134"/>
+      <c r="O3" s="172"/>
+      <c r="P3" s="172"/>
+      <c r="Q3" s="172"/>
+      <c r="R3" s="172"/>
+      <c r="S3" s="172"/>
+      <c r="T3" s="172"/>
+      <c r="U3" s="172"/>
+      <c r="V3" s="172"/>
+      <c r="W3" s="172"/>
+      <c r="X3" s="172"/>
+      <c r="Y3" s="172"/>
+      <c r="Z3" s="172"/>
+      <c r="AA3" s="172"/>
+      <c r="AB3" s="172"/>
+      <c r="AC3" s="172"/>
     </row>
     <row r="4" spans="1:29" ht="13.5" customHeight="1">
       <c r="A4" s="1"/>
@@ -4041,22 +3728,22 @@
       <c r="K4" s="1"/>
       <c r="L4" s="1"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="134"/>
-      <c r="O4" s="134"/>
-      <c r="P4" s="134"/>
-      <c r="Q4" s="134"/>
-      <c r="R4" s="134"/>
-      <c r="S4" s="134"/>
-      <c r="T4" s="134"/>
-      <c r="U4" s="134"/>
-      <c r="V4" s="134"/>
-      <c r="W4" s="134"/>
-      <c r="X4" s="134"/>
-      <c r="Y4" s="134"/>
-      <c r="Z4" s="134"/>
-      <c r="AA4" s="134"/>
-      <c r="AB4" s="134"/>
-      <c r="AC4" s="134"/>
+      <c r="N4" s="172"/>
+      <c r="O4" s="172"/>
+      <c r="P4" s="172"/>
+      <c r="Q4" s="172"/>
+      <c r="R4" s="172"/>
+      <c r="S4" s="172"/>
+      <c r="T4" s="172"/>
+      <c r="U4" s="172"/>
+      <c r="V4" s="172"/>
+      <c r="W4" s="172"/>
+      <c r="X4" s="172"/>
+      <c r="Y4" s="172"/>
+      <c r="Z4" s="172"/>
+      <c r="AA4" s="172"/>
+      <c r="AB4" s="172"/>
+      <c r="AC4" s="172"/>
     </row>
     <row r="5" spans="1:29" ht="13.5" customHeight="1">
       <c r="A5" s="1"/>
@@ -4072,22 +3759,22 @@
       <c r="K5" s="1"/>
       <c r="L5" s="1"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="134"/>
-      <c r="O5" s="134"/>
-      <c r="P5" s="134"/>
-      <c r="Q5" s="134"/>
-      <c r="R5" s="134"/>
-      <c r="S5" s="134"/>
-      <c r="T5" s="134"/>
-      <c r="U5" s="134"/>
-      <c r="V5" s="134"/>
-      <c r="W5" s="134"/>
-      <c r="X5" s="134"/>
-      <c r="Y5" s="134"/>
-      <c r="Z5" s="134"/>
-      <c r="AA5" s="134"/>
-      <c r="AB5" s="134"/>
-      <c r="AC5" s="134"/>
+      <c r="N5" s="172"/>
+      <c r="O5" s="172"/>
+      <c r="P5" s="172"/>
+      <c r="Q5" s="172"/>
+      <c r="R5" s="172"/>
+      <c r="S5" s="172"/>
+      <c r="T5" s="172"/>
+      <c r="U5" s="172"/>
+      <c r="V5" s="172"/>
+      <c r="W5" s="172"/>
+      <c r="X5" s="172"/>
+      <c r="Y5" s="172"/>
+      <c r="Z5" s="172"/>
+      <c r="AA5" s="172"/>
+      <c r="AB5" s="172"/>
+      <c r="AC5" s="172"/>
     </row>
     <row r="6" spans="1:29" ht="13.5" customHeight="1">
       <c r="A6" s="1"/>
@@ -4103,22 +3790,22 @@
       <c r="K6" s="1"/>
       <c r="L6" s="1"/>
       <c r="M6" s="1"/>
-      <c r="N6" s="134"/>
-      <c r="O6" s="134"/>
-      <c r="P6" s="134"/>
-      <c r="Q6" s="134"/>
-      <c r="R6" s="134"/>
-      <c r="S6" s="134"/>
-      <c r="T6" s="134"/>
-      <c r="U6" s="134"/>
-      <c r="V6" s="134"/>
-      <c r="W6" s="134"/>
-      <c r="X6" s="134"/>
-      <c r="Y6" s="134"/>
-      <c r="Z6" s="134"/>
-      <c r="AA6" s="134"/>
-      <c r="AB6" s="134"/>
-      <c r="AC6" s="134"/>
+      <c r="N6" s="172"/>
+      <c r="O6" s="172"/>
+      <c r="P6" s="172"/>
+      <c r="Q6" s="172"/>
+      <c r="R6" s="172"/>
+      <c r="S6" s="172"/>
+      <c r="T6" s="172"/>
+      <c r="U6" s="172"/>
+      <c r="V6" s="172"/>
+      <c r="W6" s="172"/>
+      <c r="X6" s="172"/>
+      <c r="Y6" s="172"/>
+      <c r="Z6" s="172"/>
+      <c r="AA6" s="172"/>
+      <c r="AB6" s="172"/>
+      <c r="AC6" s="172"/>
     </row>
     <row r="7" spans="1:29" ht="13.5" customHeight="1">
       <c r="A7" s="1"/>
@@ -4148,22 +3835,22 @@
       <c r="K7" s="1"/>
       <c r="L7" s="1"/>
       <c r="M7" s="1"/>
-      <c r="N7" s="134"/>
-      <c r="O7" s="134"/>
-      <c r="P7" s="134"/>
-      <c r="Q7" s="134"/>
-      <c r="R7" s="134"/>
-      <c r="S7" s="134"/>
-      <c r="T7" s="134"/>
-      <c r="U7" s="134"/>
-      <c r="V7" s="134"/>
-      <c r="W7" s="134"/>
-      <c r="X7" s="134"/>
-      <c r="Y7" s="134"/>
-      <c r="Z7" s="134"/>
-      <c r="AA7" s="134"/>
-      <c r="AB7" s="134"/>
-      <c r="AC7" s="134"/>
+      <c r="N7" s="172"/>
+      <c r="O7" s="172"/>
+      <c r="P7" s="172"/>
+      <c r="Q7" s="172"/>
+      <c r="R7" s="172"/>
+      <c r="S7" s="172"/>
+      <c r="T7" s="172"/>
+      <c r="U7" s="172"/>
+      <c r="V7" s="172"/>
+      <c r="W7" s="172"/>
+      <c r="X7" s="172"/>
+      <c r="Y7" s="172"/>
+      <c r="Z7" s="172"/>
+      <c r="AA7" s="172"/>
+      <c r="AB7" s="172"/>
+      <c r="AC7" s="172"/>
     </row>
     <row r="8" spans="1:29" ht="13.5" customHeight="1">
       <c r="A8" s="1"/>
@@ -4193,57 +3880,57 @@
       <c r="K8" s="1"/>
       <c r="L8" s="1"/>
       <c r="M8" s="1"/>
-      <c r="N8" s="134"/>
-      <c r="O8" s="134"/>
-      <c r="P8" s="134"/>
-      <c r="Q8" s="134"/>
-      <c r="R8" s="134"/>
-      <c r="S8" s="134"/>
-      <c r="T8" s="134"/>
-      <c r="U8" s="134"/>
-      <c r="V8" s="134"/>
-      <c r="W8" s="134"/>
-      <c r="X8" s="134"/>
-      <c r="Y8" s="134"/>
-      <c r="Z8" s="134"/>
-      <c r="AA8" s="134"/>
-      <c r="AB8" s="134"/>
-      <c r="AC8" s="134"/>
+      <c r="N8" s="172"/>
+      <c r="O8" s="172"/>
+      <c r="P8" s="172"/>
+      <c r="Q8" s="172"/>
+      <c r="R8" s="172"/>
+      <c r="S8" s="172"/>
+      <c r="T8" s="172"/>
+      <c r="U8" s="172"/>
+      <c r="V8" s="172"/>
+      <c r="W8" s="172"/>
+      <c r="X8" s="172"/>
+      <c r="Y8" s="172"/>
+      <c r="Z8" s="172"/>
+      <c r="AA8" s="172"/>
+      <c r="AB8" s="172"/>
+      <c r="AC8" s="172"/>
     </row>
     <row r="9" spans="1:29" ht="13.5" customHeight="1">
       <c r="A9" s="1"/>
       <c r="B9" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C9" s="133" t="s">
+      <c r="C9" s="186" t="s">
         <v>13</v>
       </c>
-      <c r="D9" s="134"/>
-      <c r="E9" s="134"/>
-      <c r="F9" s="134"/>
-      <c r="G9" s="134"/>
+      <c r="D9" s="172"/>
+      <c r="E9" s="172"/>
+      <c r="F9" s="172"/>
+      <c r="G9" s="172"/>
       <c r="H9" s="5"/>
       <c r="I9" s="1"/>
       <c r="J9" s="1"/>
       <c r="K9" s="1"/>
       <c r="L9" s="1"/>
       <c r="M9" s="1"/>
-      <c r="N9" s="134"/>
-      <c r="O9" s="134"/>
-      <c r="P9" s="134"/>
-      <c r="Q9" s="134"/>
-      <c r="R9" s="134"/>
-      <c r="S9" s="134"/>
-      <c r="T9" s="134"/>
-      <c r="U9" s="134"/>
-      <c r="V9" s="134"/>
-      <c r="W9" s="134"/>
-      <c r="X9" s="134"/>
-      <c r="Y9" s="134"/>
-      <c r="Z9" s="134"/>
-      <c r="AA9" s="134"/>
-      <c r="AB9" s="134"/>
-      <c r="AC9" s="134"/>
+      <c r="N9" s="172"/>
+      <c r="O9" s="172"/>
+      <c r="P9" s="172"/>
+      <c r="Q9" s="172"/>
+      <c r="R9" s="172"/>
+      <c r="S9" s="172"/>
+      <c r="T9" s="172"/>
+      <c r="U9" s="172"/>
+      <c r="V9" s="172"/>
+      <c r="W9" s="172"/>
+      <c r="X9" s="172"/>
+      <c r="Y9" s="172"/>
+      <c r="Z9" s="172"/>
+      <c r="AA9" s="172"/>
+      <c r="AB9" s="172"/>
+      <c r="AC9" s="172"/>
     </row>
     <row r="10" spans="1:29" ht="13.5" customHeight="1">
       <c r="A10" s="1"/>
@@ -4261,22 +3948,22 @@
       <c r="K10" s="1"/>
       <c r="L10" s="1"/>
       <c r="M10" s="1"/>
-      <c r="N10" s="134"/>
-      <c r="O10" s="134"/>
-      <c r="P10" s="134"/>
-      <c r="Q10" s="134"/>
-      <c r="R10" s="134"/>
-      <c r="S10" s="134"/>
-      <c r="T10" s="134"/>
-      <c r="U10" s="134"/>
-      <c r="V10" s="134"/>
-      <c r="W10" s="134"/>
-      <c r="X10" s="134"/>
-      <c r="Y10" s="134"/>
-      <c r="Z10" s="134"/>
-      <c r="AA10" s="134"/>
-      <c r="AB10" s="134"/>
-      <c r="AC10" s="134"/>
+      <c r="N10" s="172"/>
+      <c r="O10" s="172"/>
+      <c r="P10" s="172"/>
+      <c r="Q10" s="172"/>
+      <c r="R10" s="172"/>
+      <c r="S10" s="172"/>
+      <c r="T10" s="172"/>
+      <c r="U10" s="172"/>
+      <c r="V10" s="172"/>
+      <c r="W10" s="172"/>
+      <c r="X10" s="172"/>
+      <c r="Y10" s="172"/>
+      <c r="Z10" s="172"/>
+      <c r="AA10" s="172"/>
+      <c r="AB10" s="172"/>
+      <c r="AC10" s="172"/>
     </row>
     <row r="11" spans="1:29" ht="13.5" customHeight="1">
       <c r="A11" s="1"/>
@@ -4292,22 +3979,22 @@
       <c r="K11" s="1"/>
       <c r="L11" s="1"/>
       <c r="M11" s="1"/>
-      <c r="N11" s="134"/>
-      <c r="O11" s="134"/>
-      <c r="P11" s="134"/>
-      <c r="Q11" s="134"/>
-      <c r="R11" s="134"/>
-      <c r="S11" s="134"/>
-      <c r="T11" s="134"/>
-      <c r="U11" s="134"/>
-      <c r="V11" s="134"/>
-      <c r="W11" s="134"/>
-      <c r="X11" s="134"/>
-      <c r="Y11" s="134"/>
-      <c r="Z11" s="134"/>
-      <c r="AA11" s="134"/>
-      <c r="AB11" s="134"/>
-      <c r="AC11" s="134"/>
+      <c r="N11" s="172"/>
+      <c r="O11" s="172"/>
+      <c r="P11" s="172"/>
+      <c r="Q11" s="172"/>
+      <c r="R11" s="172"/>
+      <c r="S11" s="172"/>
+      <c r="T11" s="172"/>
+      <c r="U11" s="172"/>
+      <c r="V11" s="172"/>
+      <c r="W11" s="172"/>
+      <c r="X11" s="172"/>
+      <c r="Y11" s="172"/>
+      <c r="Z11" s="172"/>
+      <c r="AA11" s="172"/>
+      <c r="AB11" s="172"/>
+      <c r="AC11" s="172"/>
     </row>
     <row r="12" spans="1:29" ht="13.5" customHeight="1">
       <c r="A12" s="1"/>
@@ -4324,22 +4011,22 @@
       <c r="K12" s="1"/>
       <c r="L12" s="25"/>
       <c r="M12" s="25"/>
-      <c r="N12" s="134"/>
-      <c r="O12" s="134"/>
-      <c r="P12" s="134"/>
-      <c r="Q12" s="134"/>
-      <c r="R12" s="134"/>
-      <c r="S12" s="134"/>
-      <c r="T12" s="134"/>
-      <c r="U12" s="134"/>
-      <c r="V12" s="134"/>
-      <c r="W12" s="134"/>
-      <c r="X12" s="134"/>
-      <c r="Y12" s="134"/>
-      <c r="Z12" s="134"/>
-      <c r="AA12" s="134"/>
-      <c r="AB12" s="134"/>
-      <c r="AC12" s="134"/>
+      <c r="N12" s="172"/>
+      <c r="O12" s="172"/>
+      <c r="P12" s="172"/>
+      <c r="Q12" s="172"/>
+      <c r="R12" s="172"/>
+      <c r="S12" s="172"/>
+      <c r="T12" s="172"/>
+      <c r="U12" s="172"/>
+      <c r="V12" s="172"/>
+      <c r="W12" s="172"/>
+      <c r="X12" s="172"/>
+      <c r="Y12" s="172"/>
+      <c r="Z12" s="172"/>
+      <c r="AA12" s="172"/>
+      <c r="AB12" s="172"/>
+      <c r="AC12" s="172"/>
     </row>
     <row r="13" spans="1:29" ht="13.5" customHeight="1">
       <c r="A13" s="1"/>
@@ -4356,22 +4043,22 @@
       <c r="K13" s="1"/>
       <c r="L13" s="25"/>
       <c r="M13" s="25"/>
-      <c r="N13" s="134"/>
-      <c r="O13" s="134"/>
-      <c r="P13" s="134"/>
-      <c r="Q13" s="134"/>
-      <c r="R13" s="134"/>
-      <c r="S13" s="134"/>
-      <c r="T13" s="134"/>
-      <c r="U13" s="134"/>
-      <c r="V13" s="134"/>
-      <c r="W13" s="134"/>
-      <c r="X13" s="134"/>
-      <c r="Y13" s="134"/>
-      <c r="Z13" s="134"/>
-      <c r="AA13" s="134"/>
-      <c r="AB13" s="134"/>
-      <c r="AC13" s="134"/>
+      <c r="N13" s="172"/>
+      <c r="O13" s="172"/>
+      <c r="P13" s="172"/>
+      <c r="Q13" s="172"/>
+      <c r="R13" s="172"/>
+      <c r="S13" s="172"/>
+      <c r="T13" s="172"/>
+      <c r="U13" s="172"/>
+      <c r="V13" s="172"/>
+      <c r="W13" s="172"/>
+      <c r="X13" s="172"/>
+      <c r="Y13" s="172"/>
+      <c r="Z13" s="172"/>
+      <c r="AA13" s="172"/>
+      <c r="AB13" s="172"/>
+      <c r="AC13" s="172"/>
     </row>
     <row r="14" spans="1:29" ht="13.5" customHeight="1">
       <c r="A14" s="1"/>
@@ -4388,22 +4075,22 @@
       <c r="K14" s="1"/>
       <c r="L14" s="25"/>
       <c r="M14" s="25"/>
-      <c r="N14" s="134"/>
-      <c r="O14" s="134"/>
-      <c r="P14" s="134"/>
-      <c r="Q14" s="134"/>
-      <c r="R14" s="134"/>
-      <c r="S14" s="134"/>
-      <c r="T14" s="134"/>
-      <c r="U14" s="134"/>
-      <c r="V14" s="134"/>
-      <c r="W14" s="134"/>
-      <c r="X14" s="134"/>
-      <c r="Y14" s="134"/>
-      <c r="Z14" s="134"/>
-      <c r="AA14" s="134"/>
-      <c r="AB14" s="134"/>
-      <c r="AC14" s="134"/>
+      <c r="N14" s="172"/>
+      <c r="O14" s="172"/>
+      <c r="P14" s="172"/>
+      <c r="Q14" s="172"/>
+      <c r="R14" s="172"/>
+      <c r="S14" s="172"/>
+      <c r="T14" s="172"/>
+      <c r="U14" s="172"/>
+      <c r="V14" s="172"/>
+      <c r="W14" s="172"/>
+      <c r="X14" s="172"/>
+      <c r="Y14" s="172"/>
+      <c r="Z14" s="172"/>
+      <c r="AA14" s="172"/>
+      <c r="AB14" s="172"/>
+      <c r="AC14" s="172"/>
     </row>
     <row r="15" spans="1:29" ht="13.5" customHeight="1">
       <c r="A15" s="1"/>
@@ -4419,240 +4106,240 @@
       <c r="K15" s="1"/>
       <c r="L15" s="1"/>
       <c r="M15" s="1"/>
-      <c r="N15" s="134"/>
-      <c r="O15" s="134"/>
-      <c r="P15" s="134"/>
-      <c r="Q15" s="134"/>
-      <c r="R15" s="134"/>
-      <c r="S15" s="134"/>
-      <c r="T15" s="134"/>
-      <c r="U15" s="134"/>
-      <c r="V15" s="134"/>
-      <c r="W15" s="134"/>
-      <c r="X15" s="134"/>
-      <c r="Y15" s="134"/>
-      <c r="Z15" s="134"/>
-      <c r="AA15" s="134"/>
-      <c r="AB15" s="134"/>
-      <c r="AC15" s="134"/>
+      <c r="N15" s="172"/>
+      <c r="O15" s="172"/>
+      <c r="P15" s="172"/>
+      <c r="Q15" s="172"/>
+      <c r="R15" s="172"/>
+      <c r="S15" s="172"/>
+      <c r="T15" s="172"/>
+      <c r="U15" s="172"/>
+      <c r="V15" s="172"/>
+      <c r="W15" s="172"/>
+      <c r="X15" s="172"/>
+      <c r="Y15" s="172"/>
+      <c r="Z15" s="172"/>
+      <c r="AA15" s="172"/>
+      <c r="AB15" s="172"/>
+      <c r="AC15" s="172"/>
     </row>
     <row r="16" spans="1:29" ht="16.5" customHeight="1">
       <c r="A16" s="1"/>
       <c r="B16" s="26" t="s">
         <v>18</v>
       </c>
-      <c r="C16" s="135" t="s">
+      <c r="C16" s="187" t="s">
         <v>19</v>
       </c>
-      <c r="D16" s="136"/>
-      <c r="E16" s="137"/>
-      <c r="F16" s="138" t="s">
+      <c r="D16" s="174"/>
+      <c r="E16" s="188"/>
+      <c r="F16" s="189" t="s">
         <v>20</v>
       </c>
-      <c r="G16" s="136"/>
-      <c r="H16" s="139"/>
+      <c r="G16" s="174"/>
+      <c r="H16" s="175"/>
       <c r="I16" s="1"/>
-      <c r="J16" s="146" t="s">
+      <c r="J16" s="173" t="s">
         <v>21</v>
       </c>
-      <c r="K16" s="136"/>
-      <c r="L16" s="139"/>
+      <c r="K16" s="174"/>
+      <c r="L16" s="175"/>
       <c r="M16" s="1"/>
-      <c r="N16" s="134"/>
-      <c r="O16" s="134"/>
-      <c r="P16" s="134"/>
-      <c r="Q16" s="134"/>
-      <c r="R16" s="134"/>
-      <c r="S16" s="134"/>
-      <c r="T16" s="134"/>
-      <c r="U16" s="134"/>
-      <c r="V16" s="134"/>
-      <c r="W16" s="134"/>
-      <c r="X16" s="134"/>
-      <c r="Y16" s="134"/>
-      <c r="Z16" s="134"/>
-      <c r="AA16" s="134"/>
-      <c r="AB16" s="134"/>
-      <c r="AC16" s="134"/>
+      <c r="N16" s="172"/>
+      <c r="O16" s="172"/>
+      <c r="P16" s="172"/>
+      <c r="Q16" s="172"/>
+      <c r="R16" s="172"/>
+      <c r="S16" s="172"/>
+      <c r="T16" s="172"/>
+      <c r="U16" s="172"/>
+      <c r="V16" s="172"/>
+      <c r="W16" s="172"/>
+      <c r="X16" s="172"/>
+      <c r="Y16" s="172"/>
+      <c r="Z16" s="172"/>
+      <c r="AA16" s="172"/>
+      <c r="AB16" s="172"/>
+      <c r="AC16" s="172"/>
     </row>
     <row r="17" spans="1:29" ht="13.5" customHeight="1">
       <c r="A17" s="1"/>
       <c r="B17" s="27" t="s">
         <v>22</v>
       </c>
-      <c r="C17" s="140">
+      <c r="C17" s="190">
         <v>0</v>
       </c>
-      <c r="D17" s="141"/>
-      <c r="E17" s="142"/>
-      <c r="F17" s="140">
+      <c r="D17" s="177"/>
+      <c r="E17" s="170"/>
+      <c r="F17" s="190">
         <v>1</v>
       </c>
-      <c r="G17" s="141"/>
-      <c r="H17" s="143"/>
+      <c r="G17" s="177"/>
+      <c r="H17" s="191"/>
       <c r="I17" s="1"/>
-      <c r="J17" s="147">
+      <c r="J17" s="176">
         <v>2</v>
       </c>
-      <c r="K17" s="141"/>
-      <c r="L17" s="148"/>
+      <c r="K17" s="177"/>
+      <c r="L17" s="178"/>
       <c r="M17" s="1"/>
-      <c r="N17" s="134"/>
-      <c r="O17" s="134"/>
-      <c r="P17" s="134"/>
-      <c r="Q17" s="134"/>
-      <c r="R17" s="134"/>
-      <c r="S17" s="134"/>
-      <c r="T17" s="134"/>
-      <c r="U17" s="134"/>
-      <c r="V17" s="134"/>
-      <c r="W17" s="134"/>
-      <c r="X17" s="134"/>
-      <c r="Y17" s="134"/>
-      <c r="Z17" s="134"/>
-      <c r="AA17" s="134"/>
-      <c r="AB17" s="134"/>
-      <c r="AC17" s="134"/>
+      <c r="N17" s="172"/>
+      <c r="O17" s="172"/>
+      <c r="P17" s="172"/>
+      <c r="Q17" s="172"/>
+      <c r="R17" s="172"/>
+      <c r="S17" s="172"/>
+      <c r="T17" s="172"/>
+      <c r="U17" s="172"/>
+      <c r="V17" s="172"/>
+      <c r="W17" s="172"/>
+      <c r="X17" s="172"/>
+      <c r="Y17" s="172"/>
+      <c r="Z17" s="172"/>
+      <c r="AA17" s="172"/>
+      <c r="AB17" s="172"/>
+      <c r="AC17" s="172"/>
     </row>
     <row r="18" spans="1:29" ht="13.5" customHeight="1">
       <c r="A18" s="1"/>
-      <c r="B18" s="149" t="s">
+      <c r="B18" s="146" t="s">
         <v>23</v>
       </c>
-      <c r="C18" s="152"/>
-      <c r="D18" s="134"/>
-      <c r="E18" s="153"/>
-      <c r="F18" s="152"/>
-      <c r="G18" s="134"/>
-      <c r="H18" s="156"/>
+      <c r="C18" s="179"/>
+      <c r="D18" s="172"/>
+      <c r="E18" s="141"/>
+      <c r="F18" s="179"/>
+      <c r="G18" s="172"/>
+      <c r="H18" s="181"/>
       <c r="I18" s="1"/>
-      <c r="J18" s="175"/>
-      <c r="K18" s="134"/>
-      <c r="L18" s="156"/>
+      <c r="J18" s="183"/>
+      <c r="K18" s="172"/>
+      <c r="L18" s="181"/>
       <c r="M18" s="1"/>
-      <c r="N18" s="134"/>
-      <c r="O18" s="134"/>
-      <c r="P18" s="134"/>
-      <c r="Q18" s="134"/>
-      <c r="R18" s="134"/>
-      <c r="S18" s="134"/>
-      <c r="T18" s="134"/>
-      <c r="U18" s="134"/>
-      <c r="V18" s="134"/>
-      <c r="W18" s="134"/>
-      <c r="X18" s="134"/>
-      <c r="Y18" s="134"/>
-      <c r="Z18" s="134"/>
-      <c r="AA18" s="134"/>
-      <c r="AB18" s="134"/>
-      <c r="AC18" s="134"/>
+      <c r="N18" s="172"/>
+      <c r="O18" s="172"/>
+      <c r="P18" s="172"/>
+      <c r="Q18" s="172"/>
+      <c r="R18" s="172"/>
+      <c r="S18" s="172"/>
+      <c r="T18" s="172"/>
+      <c r="U18" s="172"/>
+      <c r="V18" s="172"/>
+      <c r="W18" s="172"/>
+      <c r="X18" s="172"/>
+      <c r="Y18" s="172"/>
+      <c r="Z18" s="172"/>
+      <c r="AA18" s="172"/>
+      <c r="AB18" s="172"/>
+      <c r="AC18" s="172"/>
     </row>
     <row r="19" spans="1:29" ht="13.5" customHeight="1">
       <c r="A19" s="1"/>
-      <c r="B19" s="150"/>
-      <c r="C19" s="134"/>
-      <c r="D19" s="134"/>
-      <c r="E19" s="153"/>
-      <c r="F19" s="134"/>
-      <c r="G19" s="134"/>
-      <c r="H19" s="156"/>
+      <c r="B19" s="147"/>
+      <c r="C19" s="172"/>
+      <c r="D19" s="172"/>
+      <c r="E19" s="141"/>
+      <c r="F19" s="172"/>
+      <c r="G19" s="172"/>
+      <c r="H19" s="181"/>
       <c r="I19" s="1"/>
-      <c r="J19" s="176"/>
-      <c r="K19" s="134"/>
-      <c r="L19" s="156"/>
+      <c r="J19" s="184"/>
+      <c r="K19" s="172"/>
+      <c r="L19" s="181"/>
       <c r="M19" s="1"/>
-      <c r="N19" s="134"/>
-      <c r="O19" s="134"/>
-      <c r="P19" s="134"/>
-      <c r="Q19" s="134"/>
-      <c r="R19" s="134"/>
-      <c r="S19" s="134"/>
-      <c r="T19" s="134"/>
-      <c r="U19" s="134"/>
-      <c r="V19" s="134"/>
-      <c r="W19" s="134"/>
-      <c r="X19" s="134"/>
-      <c r="Y19" s="134"/>
-      <c r="Z19" s="134"/>
-      <c r="AA19" s="134"/>
-      <c r="AB19" s="134"/>
-      <c r="AC19" s="134"/>
+      <c r="N19" s="172"/>
+      <c r="O19" s="172"/>
+      <c r="P19" s="172"/>
+      <c r="Q19" s="172"/>
+      <c r="R19" s="172"/>
+      <c r="S19" s="172"/>
+      <c r="T19" s="172"/>
+      <c r="U19" s="172"/>
+      <c r="V19" s="172"/>
+      <c r="W19" s="172"/>
+      <c r="X19" s="172"/>
+      <c r="Y19" s="172"/>
+      <c r="Z19" s="172"/>
+      <c r="AA19" s="172"/>
+      <c r="AB19" s="172"/>
+      <c r="AC19" s="172"/>
     </row>
     <row r="20" spans="1:29" ht="13.5" customHeight="1">
       <c r="A20" s="1"/>
-      <c r="B20" s="150"/>
-      <c r="C20" s="134"/>
-      <c r="D20" s="134"/>
-      <c r="E20" s="153"/>
-      <c r="F20" s="134"/>
-      <c r="G20" s="134"/>
-      <c r="H20" s="156"/>
+      <c r="B20" s="147"/>
+      <c r="C20" s="172"/>
+      <c r="D20" s="172"/>
+      <c r="E20" s="141"/>
+      <c r="F20" s="172"/>
+      <c r="G20" s="172"/>
+      <c r="H20" s="181"/>
       <c r="I20" s="1"/>
-      <c r="J20" s="176"/>
-      <c r="K20" s="134"/>
-      <c r="L20" s="156"/>
+      <c r="J20" s="184"/>
+      <c r="K20" s="172"/>
+      <c r="L20" s="181"/>
       <c r="M20" s="1"/>
-      <c r="N20" s="134"/>
-      <c r="O20" s="134"/>
-      <c r="P20" s="134"/>
-      <c r="Q20" s="134"/>
-      <c r="R20" s="134"/>
-      <c r="S20" s="134"/>
-      <c r="T20" s="134"/>
-      <c r="U20" s="134"/>
-      <c r="V20" s="134"/>
-      <c r="W20" s="134"/>
-      <c r="X20" s="134"/>
-      <c r="Y20" s="134"/>
-      <c r="Z20" s="134"/>
-      <c r="AA20" s="134"/>
-      <c r="AB20" s="134"/>
-      <c r="AC20" s="134"/>
+      <c r="N20" s="172"/>
+      <c r="O20" s="172"/>
+      <c r="P20" s="172"/>
+      <c r="Q20" s="172"/>
+      <c r="R20" s="172"/>
+      <c r="S20" s="172"/>
+      <c r="T20" s="172"/>
+      <c r="U20" s="172"/>
+      <c r="V20" s="172"/>
+      <c r="W20" s="172"/>
+      <c r="X20" s="172"/>
+      <c r="Y20" s="172"/>
+      <c r="Z20" s="172"/>
+      <c r="AA20" s="172"/>
+      <c r="AB20" s="172"/>
+      <c r="AC20" s="172"/>
     </row>
     <row r="21" spans="1:29" ht="13.5" customHeight="1">
       <c r="A21" s="1"/>
-      <c r="B21" s="150"/>
-      <c r="C21" s="134"/>
-      <c r="D21" s="134"/>
-      <c r="E21" s="153"/>
-      <c r="F21" s="134"/>
-      <c r="G21" s="134"/>
-      <c r="H21" s="156"/>
+      <c r="B21" s="147"/>
+      <c r="C21" s="172"/>
+      <c r="D21" s="172"/>
+      <c r="E21" s="141"/>
+      <c r="F21" s="172"/>
+      <c r="G21" s="172"/>
+      <c r="H21" s="181"/>
       <c r="I21" s="1"/>
-      <c r="J21" s="176"/>
-      <c r="K21" s="134"/>
-      <c r="L21" s="156"/>
+      <c r="J21" s="184"/>
+      <c r="K21" s="172"/>
+      <c r="L21" s="181"/>
       <c r="M21" s="1"/>
-      <c r="N21" s="134"/>
-      <c r="O21" s="134"/>
-      <c r="P21" s="134"/>
-      <c r="Q21" s="134"/>
-      <c r="R21" s="134"/>
-      <c r="S21" s="134"/>
-      <c r="T21" s="134"/>
-      <c r="U21" s="134"/>
-      <c r="V21" s="134"/>
-      <c r="W21" s="134"/>
-      <c r="X21" s="134"/>
-      <c r="Y21" s="134"/>
-      <c r="Z21" s="134"/>
-      <c r="AA21" s="134"/>
-      <c r="AB21" s="134"/>
-      <c r="AC21" s="134"/>
+      <c r="N21" s="172"/>
+      <c r="O21" s="172"/>
+      <c r="P21" s="172"/>
+      <c r="Q21" s="172"/>
+      <c r="R21" s="172"/>
+      <c r="S21" s="172"/>
+      <c r="T21" s="172"/>
+      <c r="U21" s="172"/>
+      <c r="V21" s="172"/>
+      <c r="W21" s="172"/>
+      <c r="X21" s="172"/>
+      <c r="Y21" s="172"/>
+      <c r="Z21" s="172"/>
+      <c r="AA21" s="172"/>
+      <c r="AB21" s="172"/>
+      <c r="AC21" s="172"/>
     </row>
     <row r="22" spans="1:29" ht="13.5" customHeight="1">
       <c r="A22" s="1"/>
-      <c r="B22" s="150"/>
-      <c r="C22" s="134"/>
-      <c r="D22" s="134"/>
-      <c r="E22" s="153"/>
-      <c r="F22" s="134"/>
-      <c r="G22" s="134"/>
-      <c r="H22" s="156"/>
+      <c r="B22" s="147"/>
+      <c r="C22" s="172"/>
+      <c r="D22" s="172"/>
+      <c r="E22" s="141"/>
+      <c r="F22" s="172"/>
+      <c r="G22" s="172"/>
+      <c r="H22" s="181"/>
       <c r="I22" s="1"/>
-      <c r="J22" s="176"/>
-      <c r="K22" s="134"/>
-      <c r="L22" s="156"/>
+      <c r="J22" s="184"/>
+      <c r="K22" s="172"/>
+      <c r="L22" s="181"/>
       <c r="M22" s="1"/>
       <c r="N22" s="1"/>
       <c r="O22" s="1"/>
@@ -4673,17 +4360,17 @@
     </row>
     <row r="23" spans="1:29" ht="13.5" customHeight="1">
       <c r="A23" s="1"/>
-      <c r="B23" s="150"/>
-      <c r="C23" s="134"/>
-      <c r="D23" s="134"/>
-      <c r="E23" s="153"/>
-      <c r="F23" s="134"/>
-      <c r="G23" s="134"/>
-      <c r="H23" s="156"/>
+      <c r="B23" s="147"/>
+      <c r="C23" s="172"/>
+      <c r="D23" s="172"/>
+      <c r="E23" s="141"/>
+      <c r="F23" s="172"/>
+      <c r="G23" s="172"/>
+      <c r="H23" s="181"/>
       <c r="I23" s="1"/>
-      <c r="J23" s="176"/>
-      <c r="K23" s="134"/>
-      <c r="L23" s="156"/>
+      <c r="J23" s="184"/>
+      <c r="K23" s="172"/>
+      <c r="L23" s="181"/>
       <c r="M23" s="1"/>
       <c r="N23" s="1"/>
       <c r="O23" s="1"/>
@@ -4704,17 +4391,17 @@
     </row>
     <row r="24" spans="1:29" ht="13.5" customHeight="1">
       <c r="A24" s="1"/>
-      <c r="B24" s="151"/>
-      <c r="C24" s="154"/>
-      <c r="D24" s="154"/>
-      <c r="E24" s="155"/>
-      <c r="F24" s="154"/>
-      <c r="G24" s="154"/>
-      <c r="H24" s="157"/>
+      <c r="B24" s="148"/>
+      <c r="C24" s="180"/>
+      <c r="D24" s="180"/>
+      <c r="E24" s="142"/>
+      <c r="F24" s="180"/>
+      <c r="G24" s="180"/>
+      <c r="H24" s="182"/>
       <c r="I24" s="1"/>
-      <c r="J24" s="177"/>
-      <c r="K24" s="154"/>
-      <c r="L24" s="157"/>
+      <c r="J24" s="185"/>
+      <c r="K24" s="180"/>
+      <c r="L24" s="182"/>
       <c r="M24" s="1"/>
       <c r="N24" s="1"/>
       <c r="O24" s="1"/>
@@ -4738,24 +4425,24 @@
       <c r="B25" s="28">
         <v>6</v>
       </c>
-      <c r="C25" s="158" t="s">
+      <c r="C25" s="163" t="s">
         <v>24</v>
       </c>
-      <c r="D25" s="159"/>
-      <c r="E25" s="160"/>
-      <c r="F25" s="158" t="s">
+      <c r="D25" s="164"/>
+      <c r="E25" s="151"/>
+      <c r="F25" s="163" t="s">
         <v>24</v>
       </c>
-      <c r="G25" s="159"/>
-      <c r="H25" s="161"/>
+      <c r="G25" s="164"/>
+      <c r="H25" s="165"/>
       <c r="I25" s="1"/>
       <c r="J25" s="29" t="s">
         <v>25</v>
       </c>
-      <c r="K25" s="178">
+      <c r="K25" s="150">
         <v>100</v>
       </c>
-      <c r="L25" s="160"/>
+      <c r="L25" s="151"/>
       <c r="M25" s="1"/>
       <c r="N25" s="1"/>
       <c r="O25" s="1"/>
@@ -4779,24 +4466,24 @@
       <c r="B26" s="30">
         <v>5</v>
       </c>
-      <c r="C26" s="162" t="s">
+      <c r="C26" s="166" t="s">
         <v>24</v>
       </c>
-      <c r="D26" s="163"/>
-      <c r="E26" s="164"/>
-      <c r="F26" s="162" t="s">
+      <c r="D26" s="167"/>
+      <c r="E26" s="153"/>
+      <c r="F26" s="166" t="s">
         <v>24</v>
       </c>
-      <c r="G26" s="163"/>
-      <c r="H26" s="165"/>
+      <c r="G26" s="167"/>
+      <c r="H26" s="168"/>
       <c r="I26" s="1"/>
       <c r="J26" s="31" t="s">
         <v>26</v>
       </c>
-      <c r="K26" s="173">
+      <c r="K26" s="152">
         <v>40</v>
       </c>
-      <c r="L26" s="164"/>
+      <c r="L26" s="153"/>
       <c r="M26" s="1"/>
       <c r="N26" s="1"/>
       <c r="O26" s="1"/>
@@ -4820,24 +4507,24 @@
       <c r="B27" s="30">
         <v>4</v>
       </c>
-      <c r="C27" s="162" t="s">
+      <c r="C27" s="166" t="s">
         <v>24</v>
       </c>
-      <c r="D27" s="163"/>
-      <c r="E27" s="164"/>
-      <c r="F27" s="162" t="s">
+      <c r="D27" s="167"/>
+      <c r="E27" s="153"/>
+      <c r="F27" s="166" t="s">
         <v>24</v>
       </c>
-      <c r="G27" s="163"/>
-      <c r="H27" s="165"/>
+      <c r="G27" s="167"/>
+      <c r="H27" s="168"/>
       <c r="I27" s="1"/>
       <c r="J27" s="31" t="s">
         <v>27</v>
       </c>
-      <c r="K27" s="173">
+      <c r="K27" s="152">
         <v>20</v>
       </c>
-      <c r="L27" s="164"/>
+      <c r="L27" s="153"/>
       <c r="M27" s="1"/>
       <c r="N27" s="1"/>
       <c r="O27" s="1"/>
@@ -4861,24 +4548,24 @@
       <c r="B28" s="32">
         <v>3</v>
       </c>
-      <c r="C28" s="166" t="s">
+      <c r="C28" s="154" t="s">
         <v>24</v>
       </c>
-      <c r="D28" s="167"/>
-      <c r="E28" s="168"/>
-      <c r="F28" s="166" t="s">
+      <c r="D28" s="155"/>
+      <c r="E28" s="156"/>
+      <c r="F28" s="154" t="s">
         <v>24</v>
       </c>
-      <c r="G28" s="167"/>
-      <c r="H28" s="169"/>
+      <c r="G28" s="155"/>
+      <c r="H28" s="157"/>
       <c r="I28" s="1"/>
       <c r="J28" s="31" t="s">
         <v>28</v>
       </c>
-      <c r="K28" s="173">
+      <c r="K28" s="152">
         <v>10</v>
       </c>
-      <c r="L28" s="164"/>
+      <c r="L28" s="153"/>
       <c r="M28" s="1"/>
       <c r="N28" s="1"/>
       <c r="O28" s="1"/>
@@ -4899,21 +4586,21 @@
     </row>
     <row r="29" spans="1:29" ht="13.5" customHeight="1">
       <c r="A29" s="1"/>
-      <c r="B29" s="170"/>
-      <c r="C29" s="171"/>
-      <c r="D29" s="171"/>
-      <c r="E29" s="171"/>
-      <c r="F29" s="171"/>
-      <c r="G29" s="171"/>
-      <c r="H29" s="172"/>
+      <c r="B29" s="158"/>
+      <c r="C29" s="144"/>
+      <c r="D29" s="144"/>
+      <c r="E29" s="144"/>
+      <c r="F29" s="144"/>
+      <c r="G29" s="144"/>
+      <c r="H29" s="145"/>
       <c r="I29" s="1"/>
       <c r="J29" s="31" t="s">
         <v>29</v>
       </c>
-      <c r="K29" s="173">
+      <c r="K29" s="152">
         <v>6</v>
       </c>
-      <c r="L29" s="164"/>
+      <c r="L29" s="153"/>
       <c r="M29" s="1"/>
       <c r="N29" s="1"/>
       <c r="O29" s="1"/>
@@ -4959,10 +4646,10 @@
       <c r="J30" s="31" t="s">
         <v>36</v>
       </c>
-      <c r="K30" s="173">
+      <c r="K30" s="152">
         <v>3</v>
       </c>
-      <c r="L30" s="164"/>
+      <c r="L30" s="153"/>
       <c r="M30" s="1"/>
       <c r="N30" s="1"/>
       <c r="O30" s="1"/>
@@ -5008,10 +4695,10 @@
       <c r="J31" s="31" t="s">
         <v>37</v>
       </c>
-      <c r="K31" s="173">
+      <c r="K31" s="152">
         <v>2</v>
       </c>
-      <c r="L31" s="164"/>
+      <c r="L31" s="153"/>
       <c r="M31" s="1"/>
       <c r="N31" s="1"/>
       <c r="O31" s="1"/>
@@ -5032,23 +4719,23 @@
     </row>
     <row r="32" spans="1:29" ht="13.5" customHeight="1">
       <c r="A32" s="1"/>
-      <c r="B32" s="179" t="s">
+      <c r="B32" s="160" t="s">
         <v>23</v>
       </c>
-      <c r="C32" s="183"/>
-      <c r="D32" s="183"/>
-      <c r="E32" s="183"/>
-      <c r="F32" s="183"/>
-      <c r="G32" s="186"/>
-      <c r="H32" s="190"/>
+      <c r="C32" s="139"/>
+      <c r="D32" s="139"/>
+      <c r="E32" s="139"/>
+      <c r="F32" s="139"/>
+      <c r="G32" s="133"/>
+      <c r="H32" s="140"/>
       <c r="I32" s="1"/>
       <c r="J32" s="41" t="s">
         <v>38</v>
       </c>
-      <c r="K32" s="174">
+      <c r="K32" s="159">
         <v>1</v>
       </c>
-      <c r="L32" s="168"/>
+      <c r="L32" s="156"/>
       <c r="M32" s="1"/>
       <c r="N32" s="1"/>
       <c r="O32" s="1"/>
@@ -5069,13 +4756,13 @@
     </row>
     <row r="33" spans="1:29" ht="13.5" customHeight="1">
       <c r="A33" s="1"/>
-      <c r="B33" s="180"/>
-      <c r="C33" s="184"/>
-      <c r="D33" s="184"/>
-      <c r="E33" s="184"/>
-      <c r="F33" s="184"/>
-      <c r="G33" s="184"/>
-      <c r="H33" s="153"/>
+      <c r="B33" s="161"/>
+      <c r="C33" s="134"/>
+      <c r="D33" s="134"/>
+      <c r="E33" s="134"/>
+      <c r="F33" s="134"/>
+      <c r="G33" s="134"/>
+      <c r="H33" s="141"/>
       <c r="I33" s="1"/>
       <c r="J33" s="1"/>
       <c r="K33" s="1"/>
@@ -5100,13 +4787,13 @@
     </row>
     <row r="34" spans="1:29" ht="13.5" customHeight="1">
       <c r="A34" s="1"/>
-      <c r="B34" s="180"/>
-      <c r="C34" s="184"/>
-      <c r="D34" s="184"/>
-      <c r="E34" s="184"/>
-      <c r="F34" s="184"/>
-      <c r="G34" s="184"/>
-      <c r="H34" s="153"/>
+      <c r="B34" s="161"/>
+      <c r="C34" s="134"/>
+      <c r="D34" s="134"/>
+      <c r="E34" s="134"/>
+      <c r="F34" s="134"/>
+      <c r="G34" s="134"/>
+      <c r="H34" s="141"/>
       <c r="I34" s="1"/>
       <c r="J34" s="1"/>
       <c r="K34" s="1"/>
@@ -5131,13 +4818,13 @@
     </row>
     <row r="35" spans="1:29" ht="13.5" customHeight="1">
       <c r="A35" s="1"/>
-      <c r="B35" s="180"/>
-      <c r="C35" s="184"/>
-      <c r="D35" s="184"/>
-      <c r="E35" s="184"/>
-      <c r="F35" s="184"/>
-      <c r="G35" s="184"/>
-      <c r="H35" s="153"/>
+      <c r="B35" s="161"/>
+      <c r="C35" s="134"/>
+      <c r="D35" s="134"/>
+      <c r="E35" s="134"/>
+      <c r="F35" s="134"/>
+      <c r="G35" s="134"/>
+      <c r="H35" s="141"/>
       <c r="I35" s="1"/>
       <c r="J35" s="1"/>
       <c r="K35" s="1"/>
@@ -5162,13 +4849,13 @@
     </row>
     <row r="36" spans="1:29" ht="13.5" customHeight="1">
       <c r="A36" s="1"/>
-      <c r="B36" s="181"/>
-      <c r="C36" s="185"/>
-      <c r="D36" s="185"/>
-      <c r="E36" s="185"/>
-      <c r="F36" s="185"/>
-      <c r="G36" s="185"/>
-      <c r="H36" s="155"/>
+      <c r="B36" s="162"/>
+      <c r="C36" s="135"/>
+      <c r="D36" s="135"/>
+      <c r="E36" s="135"/>
+      <c r="F36" s="135"/>
+      <c r="G36" s="135"/>
+      <c r="H36" s="142"/>
       <c r="I36" s="1"/>
       <c r="J36" s="1"/>
       <c r="K36" s="1"/>
@@ -5357,13 +5044,13 @@
     </row>
     <row r="41" spans="1:29" ht="13.5" customHeight="1">
       <c r="A41" s="1"/>
-      <c r="B41" s="191"/>
-      <c r="C41" s="171"/>
-      <c r="D41" s="171"/>
-      <c r="E41" s="171"/>
-      <c r="F41" s="171"/>
-      <c r="G41" s="171"/>
-      <c r="H41" s="172"/>
+      <c r="B41" s="143"/>
+      <c r="C41" s="144"/>
+      <c r="D41" s="144"/>
+      <c r="E41" s="144"/>
+      <c r="F41" s="144"/>
+      <c r="G41" s="144"/>
+      <c r="H41" s="145"/>
       <c r="I41" s="1"/>
       <c r="J41" s="1"/>
       <c r="K41" s="1"/>
@@ -5478,15 +5165,15 @@
     </row>
     <row r="44" spans="1:29" ht="13.5" customHeight="1">
       <c r="A44" s="1"/>
-      <c r="B44" s="149" t="s">
+      <c r="B44" s="146" t="s">
         <v>23</v>
       </c>
-      <c r="C44" s="182"/>
-      <c r="D44" s="183"/>
-      <c r="E44" s="183"/>
-      <c r="F44" s="183"/>
-      <c r="G44" s="186"/>
-      <c r="H44" s="187"/>
+      <c r="C44" s="149"/>
+      <c r="D44" s="139"/>
+      <c r="E44" s="139"/>
+      <c r="F44" s="139"/>
+      <c r="G44" s="133"/>
+      <c r="H44" s="136"/>
       <c r="I44" s="1"/>
       <c r="J44" s="1"/>
       <c r="K44" s="1"/>
@@ -5511,13 +5198,13 @@
     </row>
     <row r="45" spans="1:29" ht="13.5" customHeight="1">
       <c r="A45" s="1"/>
-      <c r="B45" s="150"/>
-      <c r="C45" s="153"/>
-      <c r="D45" s="184"/>
-      <c r="E45" s="184"/>
-      <c r="F45" s="184"/>
-      <c r="G45" s="184"/>
-      <c r="H45" s="188"/>
+      <c r="B45" s="147"/>
+      <c r="C45" s="141"/>
+      <c r="D45" s="134"/>
+      <c r="E45" s="134"/>
+      <c r="F45" s="134"/>
+      <c r="G45" s="134"/>
+      <c r="H45" s="137"/>
       <c r="I45" s="1"/>
       <c r="J45" s="1"/>
       <c r="K45" s="1"/>
@@ -5542,13 +5229,13 @@
     </row>
     <row r="46" spans="1:29" ht="13.5" customHeight="1">
       <c r="A46" s="1"/>
-      <c r="B46" s="150"/>
-      <c r="C46" s="153"/>
-      <c r="D46" s="184"/>
-      <c r="E46" s="184"/>
-      <c r="F46" s="184"/>
-      <c r="G46" s="184"/>
-      <c r="H46" s="188"/>
+      <c r="B46" s="147"/>
+      <c r="C46" s="141"/>
+      <c r="D46" s="134"/>
+      <c r="E46" s="134"/>
+      <c r="F46" s="134"/>
+      <c r="G46" s="134"/>
+      <c r="H46" s="137"/>
       <c r="I46" s="1"/>
       <c r="J46" s="1"/>
       <c r="K46" s="1"/>
@@ -5573,13 +5260,13 @@
     </row>
     <row r="47" spans="1:29" ht="13.5" customHeight="1">
       <c r="A47" s="1"/>
-      <c r="B47" s="150"/>
-      <c r="C47" s="153"/>
-      <c r="D47" s="184"/>
-      <c r="E47" s="184"/>
-      <c r="F47" s="184"/>
-      <c r="G47" s="184"/>
-      <c r="H47" s="188"/>
+      <c r="B47" s="147"/>
+      <c r="C47" s="141"/>
+      <c r="D47" s="134"/>
+      <c r="E47" s="134"/>
+      <c r="F47" s="134"/>
+      <c r="G47" s="134"/>
+      <c r="H47" s="137"/>
       <c r="I47" s="1"/>
       <c r="J47" s="1"/>
       <c r="K47" s="1"/>
@@ -5604,13 +5291,13 @@
     </row>
     <row r="48" spans="1:29" ht="13.5" customHeight="1">
       <c r="A48" s="1"/>
-      <c r="B48" s="151"/>
-      <c r="C48" s="155"/>
-      <c r="D48" s="185"/>
-      <c r="E48" s="185"/>
-      <c r="F48" s="185"/>
-      <c r="G48" s="185"/>
-      <c r="H48" s="189"/>
+      <c r="B48" s="148"/>
+      <c r="C48" s="142"/>
+      <c r="D48" s="135"/>
+      <c r="E48" s="135"/>
+      <c r="F48" s="135"/>
+      <c r="G48" s="135"/>
+      <c r="H48" s="138"/>
       <c r="I48" s="1"/>
       <c r="J48" s="1"/>
       <c r="K48" s="1"/>
@@ -34629,6 +34316,37 @@
     </row>
   </sheetData>
   <mergeCells count="45">
+    <mergeCell ref="N2:O2"/>
+    <mergeCell ref="N3:AC21"/>
+    <mergeCell ref="J16:L16"/>
+    <mergeCell ref="J17:L17"/>
+    <mergeCell ref="B18:B24"/>
+    <mergeCell ref="C18:E24"/>
+    <mergeCell ref="F18:H24"/>
+    <mergeCell ref="J18:L24"/>
+    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="C16:E16"/>
+    <mergeCell ref="F16:H16"/>
+    <mergeCell ref="C17:E17"/>
+    <mergeCell ref="F17:H17"/>
+    <mergeCell ref="C25:E25"/>
+    <mergeCell ref="F25:H25"/>
+    <mergeCell ref="C26:E26"/>
+    <mergeCell ref="F26:H26"/>
+    <mergeCell ref="C27:E27"/>
+    <mergeCell ref="F27:H27"/>
+    <mergeCell ref="C28:E28"/>
+    <mergeCell ref="F28:H28"/>
+    <mergeCell ref="B29:H29"/>
+    <mergeCell ref="K31:L31"/>
+    <mergeCell ref="K32:L32"/>
+    <mergeCell ref="K30:L30"/>
+    <mergeCell ref="B32:B36"/>
+    <mergeCell ref="K25:L25"/>
+    <mergeCell ref="K26:L26"/>
+    <mergeCell ref="K27:L27"/>
+    <mergeCell ref="K28:L28"/>
+    <mergeCell ref="K29:L29"/>
     <mergeCell ref="G44:G48"/>
     <mergeCell ref="H44:H48"/>
     <mergeCell ref="C32:C36"/>
@@ -34643,42 +34361,10 @@
     <mergeCell ref="D44:D48"/>
     <mergeCell ref="E44:E48"/>
     <mergeCell ref="F44:F48"/>
-    <mergeCell ref="K25:L25"/>
-    <mergeCell ref="K26:L26"/>
-    <mergeCell ref="K27:L27"/>
-    <mergeCell ref="K28:L28"/>
-    <mergeCell ref="K29:L29"/>
-    <mergeCell ref="C28:E28"/>
-    <mergeCell ref="F28:H28"/>
-    <mergeCell ref="B29:H29"/>
-    <mergeCell ref="K31:L31"/>
-    <mergeCell ref="K32:L32"/>
-    <mergeCell ref="K30:L30"/>
-    <mergeCell ref="B32:B36"/>
-    <mergeCell ref="C25:E25"/>
-    <mergeCell ref="F25:H25"/>
-    <mergeCell ref="C26:E26"/>
-    <mergeCell ref="F26:H26"/>
-    <mergeCell ref="C27:E27"/>
-    <mergeCell ref="F27:H27"/>
-    <mergeCell ref="N2:O2"/>
-    <mergeCell ref="N3:AC21"/>
-    <mergeCell ref="J16:L16"/>
-    <mergeCell ref="J17:L17"/>
-    <mergeCell ref="B18:B24"/>
-    <mergeCell ref="C18:E24"/>
-    <mergeCell ref="F18:H24"/>
-    <mergeCell ref="J18:L24"/>
-    <mergeCell ref="C9:G9"/>
-    <mergeCell ref="C16:E16"/>
-    <mergeCell ref="F16:H16"/>
-    <mergeCell ref="C17:E17"/>
-    <mergeCell ref="F17:H17"/>
   </mergeCells>
   <phoneticPr fontId="39" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -34724,12 +34410,12 @@
       <c r="I2" s="63"/>
       <c r="J2" s="63"/>
       <c r="L2" s="194"/>
-      <c r="M2" s="134"/>
+      <c r="M2" s="172"/>
       <c r="N2" s="194"/>
-      <c r="O2" s="134"/>
-      <c r="P2" s="134"/>
-      <c r="Q2" s="134"/>
-      <c r="R2" s="134"/>
+      <c r="O2" s="172"/>
+      <c r="P2" s="172"/>
+      <c r="Q2" s="172"/>
+      <c r="R2" s="172"/>
     </row>
     <row r="3" spans="2:18">
       <c r="B3" s="65" t="s">
@@ -37686,12 +37372,12 @@
       <c r="J2" s="63"/>
       <c r="K2" s="63"/>
       <c r="N2" s="194"/>
-      <c r="O2" s="134"/>
+      <c r="O2" s="172"/>
       <c r="P2" s="194"/>
-      <c r="Q2" s="134"/>
-      <c r="R2" s="134"/>
-      <c r="S2" s="134"/>
-      <c r="T2" s="134"/>
+      <c r="Q2" s="172"/>
+      <c r="R2" s="172"/>
+      <c r="S2" s="172"/>
+      <c r="T2" s="172"/>
     </row>
     <row r="3" spans="2:21">
       <c r="B3" s="93" t="s">
@@ -40849,7 +40535,7 @@
       <c r="Z5" s="112"/>
     </row>
     <row r="6" spans="1:26">
-      <c r="A6" s="134"/>
+      <c r="A6" s="172"/>
       <c r="B6" s="119" t="s">
         <v>63</v>
       </c>
@@ -68698,6 +68384,6 @@
   </mergeCells>
   <phoneticPr fontId="39" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
-  <pageSetup orientation="landscape"/>
+  <pageSetup orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>